--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.818297079278</v>
+        <v>7.282973275382675</v>
       </c>
       <c r="D2" t="n">
-        <v>57.61746825418634</v>
+        <v>9.36283859130528</v>
       </c>
       <c r="E2" t="n">
-        <v>17.34448829363958</v>
+        <v>2.818479347716431</v>
       </c>
       <c r="F2" t="n">
-        <v>16.53159641419372</v>
+        <v>2.68638441730648</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.46928169097352</v>
+        <v>4.626258274783197</v>
       </c>
       <c r="D3" t="n">
-        <v>51.10207921405939</v>
+        <v>8.304087872284651</v>
       </c>
       <c r="E3" t="n">
-        <v>17.34448829363958</v>
+        <v>2.818479347716431</v>
       </c>
       <c r="F3" t="n">
-        <v>16.53159641419372</v>
+        <v>2.68638441730648</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.69237919704229</v>
+        <v>4.987511619519372</v>
       </c>
       <c r="D4" t="n">
-        <v>37.11660567270621</v>
+        <v>6.03144842181476</v>
       </c>
       <c r="E4" t="n">
-        <v>17.34448829363958</v>
+        <v>2.818479347716431</v>
       </c>
       <c r="F4" t="n">
-        <v>16.53159641419372</v>
+        <v>2.68638441730648</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.58336953776565</v>
+        <v>2.694797549886919</v>
       </c>
       <c r="D5" t="n">
-        <v>25.40388171555701</v>
+        <v>4.128130778778014</v>
       </c>
       <c r="E5" t="n">
-        <v>17.34448829363958</v>
+        <v>2.818479347716431</v>
       </c>
       <c r="F5" t="n">
-        <v>16.53159641419372</v>
+        <v>2.68638441730648</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.31300056749533</v>
+        <v>4.438362592217991</v>
       </c>
       <c r="D6" t="n">
-        <v>50.87113621691578</v>
+        <v>8.266559635248814</v>
       </c>
       <c r="E6" t="n">
-        <v>17.34448829363958</v>
+        <v>2.818479347716431</v>
       </c>
       <c r="F6" t="n">
-        <v>16.53159641419372</v>
+        <v>2.68638441730648</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9.192388155425117</v>
+        <v>1.493763075256582</v>
       </c>
       <c r="D7" t="n">
-        <v>32.89411041508799</v>
+        <v>5.345292942451799</v>
       </c>
       <c r="E7" t="n">
-        <v>17.34448829363958</v>
+        <v>2.818479347716431</v>
       </c>
       <c r="F7" t="n">
-        <v>16.53159641419372</v>
+        <v>2.68638441730648</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>9.5524865872714</v>
+        <v>1.552279070431603</v>
       </c>
       <c r="D8" t="n">
-        <v>14.58107368305115</v>
+        <v>2.369424473495812</v>
       </c>
       <c r="E8" t="n">
-        <v>17.34448829363958</v>
+        <v>2.818479347716431</v>
       </c>
       <c r="F8" t="n">
-        <v>16.53159641419372</v>
+        <v>2.68638441730648</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>10.29190320615863</v>
+        <v>1.672434271000777</v>
       </c>
       <c r="D9" t="n">
-        <v>13.88605415515869</v>
+        <v>2.256483800213287</v>
       </c>
       <c r="E9" t="n">
-        <v>17.34448829363958</v>
+        <v>2.818479347716431</v>
       </c>
       <c r="F9" t="n">
-        <v>16.53159641419372</v>
+        <v>2.68638441730648</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>14.46869118791877</v>
+        <v>2.3511623180368</v>
       </c>
       <c r="D10" t="n">
-        <v>17.75384587096206</v>
+        <v>2.884999954031335</v>
       </c>
       <c r="E10" t="n">
-        <v>17.34448829363958</v>
+        <v>2.818479347716431</v>
       </c>
       <c r="F10" t="n">
-        <v>16.53159641419372</v>
+        <v>2.68638441730648</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>38.92377554297825</v>
+        <v>6.325113525733966</v>
       </c>
       <c r="D11" t="n">
-        <v>42.40015249487452</v>
+        <v>6.890024780417109</v>
       </c>
       <c r="E11" t="n">
-        <v>17.34448829363958</v>
+        <v>2.818479347716431</v>
       </c>
       <c r="F11" t="n">
-        <v>16.53159641419372</v>
+        <v>2.68638441730648</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>46.44245725650877</v>
+        <v>7.546899304182675</v>
       </c>
       <c r="D12" t="n">
-        <v>46.94913440397658</v>
+        <v>7.629234340646194</v>
       </c>
       <c r="E12" t="n">
-        <v>17.34448829363958</v>
+        <v>2.818479347716431</v>
       </c>
       <c r="F12" t="n">
-        <v>16.53159641419372</v>
+        <v>2.68638441730648</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>68.80360153656623</v>
+        <v>11.18058524969201</v>
       </c>
       <c r="D13" t="n">
-        <v>69.37213064982291</v>
+        <v>11.27297123059622</v>
       </c>
       <c r="E13" t="n">
-        <v>17.34448829363958</v>
+        <v>2.818479347716431</v>
       </c>
       <c r="F13" t="n">
-        <v>16.53159641419372</v>
+        <v>2.68638441730648</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>42.84438798402444</v>
+        <v>6.962213047403971</v>
       </c>
       <c r="D14" t="n">
-        <v>43.31346076080497</v>
+        <v>7.038437373630808</v>
       </c>
       <c r="E14" t="n">
-        <v>17.34448829363958</v>
+        <v>2.818479347716431</v>
       </c>
       <c r="F14" t="n">
-        <v>16.53159641419372</v>
+        <v>2.68638441730648</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
